--- a/tasks/finalpool/sf-wc-order-reconciliation-excel-word-email/groundtruth_workspace/Order_Reconciliation_Report.xlsx
+++ b/tasks/finalpool/sf-wc-order-reconciliation-excel-word-email/groundtruth_workspace/Order_Reconciliation_Report.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total_Orders</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total_Revenue</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Avg_Order_Value</t>
         </is>
@@ -448,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>4198</v>
       </c>
       <c r="C2" t="n">
-        <v>320000</v>
+        <v>642644.8100000001</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="3">
@@ -464,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="C3" t="n">
-        <v>340000</v>
+        <v>648798.47</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>158.24</v>
       </c>
     </row>
     <row r="4">
@@ -480,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3500</v>
+        <v>3697</v>
       </c>
       <c r="C4" t="n">
-        <v>280000</v>
+        <v>549129.15</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>148.53</v>
       </c>
     </row>
     <row r="5">
@@ -496,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3800</v>
+        <v>3872</v>
       </c>
       <c r="C5" t="n">
-        <v>304000</v>
+        <v>602107.55</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="6">
@@ -512,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4200</v>
+        <v>4133</v>
       </c>
       <c r="C6" t="n">
-        <v>378000</v>
+        <v>606318.35</v>
       </c>
       <c r="D6" t="n">
-        <v>90</v>
+        <v>146.7</v>
       </c>
     </row>
   </sheetData>
@@ -536,17 +540,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Order_Count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total_Amount</t>
         </is>
@@ -559,10 +563,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>5000</v>
+        <v>4547.42</v>
       </c>
     </row>
     <row r="3">
@@ -572,10 +576,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>60000</v>
+        <v>30296.82</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +592,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2500</v>
+        <v>2130.43</v>
       </c>
     </row>
     <row r="5">
@@ -598,10 +602,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>8000</v>
+        <v>6845.7</v>
       </c>
     </row>
     <row r="6">
@@ -611,10 +615,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>12000</v>
+        <v>4514.01</v>
       </c>
     </row>
     <row r="7">
@@ -624,10 +628,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>20000</v>
+        <v>9121.35</v>
       </c>
     </row>
     <row r="8">
@@ -637,10 +641,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>8000</v>
+        <v>4256.31</v>
       </c>
     </row>
   </sheetData>
@@ -658,22 +662,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DW_Value</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Store_Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -686,13 +690,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1622000</v>
+        <v>3048998.33</v>
       </c>
       <c r="C2" t="n">
-        <v>115500</v>
+        <v>61712.04</v>
       </c>
       <c r="D2" t="n">
-        <v>1506500</v>
+        <v>2987286.29</v>
       </c>
     </row>
     <row r="3">
@@ -702,13 +706,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19500</v>
+        <v>20000</v>
       </c>
       <c r="C3" t="n">
         <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>19350</v>
+        <v>19850</v>
       </c>
     </row>
     <row r="4">
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83.18000000000001</v>
+        <v>152.45</v>
       </c>
       <c r="C4" t="n">
-        <v>770</v>
+        <v>411.41</v>
       </c>
       <c r="D4" t="n">
-        <v>-686.8200000000001</v>
+        <v>-258.96</v>
       </c>
     </row>
   </sheetData>
@@ -742,12 +746,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Finding</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
@@ -761,7 +765,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Data warehouse contains significantly more orders than online store</t>
+          <t>Data warehouse has 20000 orders vs 150 in the online store</t>
         </is>
       </c>
     </row>
@@ -773,7 +777,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Large discrepancy in total revenue between systems</t>
+          <t>DW total revenue $3,048,998.33 far exceeds store $61,712.04</t>
         </is>
       </c>
     </row>
@@ -785,7 +789,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Online store shows higher average due to different product mix</t>
+          <t>Store avg $411.41 is higher than DW avg $152.45 (different product mix)</t>
         </is>
       </c>
     </row>
